--- a/education_surveys/021_university_distance_learning_feedback_survey--education_surveys.xlsx
+++ b/education_surveys/021_university_distance_learning_feedback_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>other_instructor</t>
+          <t>other_instructor_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>other instructor</t>
+          <t>Other Instructor 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>other_program</t>
+          <t>other_program_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>other program</t>
+          <t>Other Program 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>other_course</t>
+          <t>other_course_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>other course</t>
+          <t>Other Course 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>other_section</t>
+          <t>other_section_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>other section</t>
+          <t>Other Section 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>other_instructor</t>
+          <t>other_instructor_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>other instructor</t>
+          <t>Other Instructor 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>other_program_choices</t>
+          <t>other_program_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>other_program_choices</t>
+          <t>other_program_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1670,7 +1670,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>other_course_choices</t>
+          <t>other_course_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1687,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>other_course_choices</t>
+          <t>other_course_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>other_section_choices</t>
+          <t>other_section_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>other_section_choices</t>
+          <t>other_section_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1738,7 +1738,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>other_instructor_choices</t>
+          <t>other_instructor_3_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1755,7 +1755,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>other_instructor_choices</t>
+          <t>other_instructor_3_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
